--- a/Result/profitability/1735.xlsx
+++ b/Result/profitability/1735.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.17625</v>
       </c>
       <c r="N2" t="n">
-        <v>16.9925</v>
+        <v>17.00375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.16125</v>
+        <v>0.15375</v>
       </c>
       <c r="N3" t="n">
-        <v>15.93625</v>
+        <v>15.99625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.12375</v>
+        <v>0.12625</v>
       </c>
       <c r="N4" t="n">
-        <v>14.2425</v>
+        <v>14.32</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>0.05375000000000001</v>
+        <v>0.09875</v>
       </c>
       <c r="N5" t="n">
-        <v>12.59375</v>
+        <v>12.95375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.19</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09875</v>
+        <v>0.0975</v>
       </c>
       <c r="N6" t="n">
-        <v>12.0725</v>
+        <v>12.1475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>0.15625</v>
+        <v>0.1075</v>
       </c>
       <c r="N7" t="n">
-        <v>11.98</v>
+        <v>11.86</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.14</v>
+        <v>0.13875</v>
       </c>
       <c r="N8" t="n">
-        <v>11.065</v>
+        <v>11.02125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.06</v>
       </c>
       <c r="M13" t="n">
-        <v>0.255</v>
+        <v>0.2550000000000001</v>
       </c>
       <c r="N13" t="n">
         <v>12.78625</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>664</v>
+      </c>
+      <c r="D75" t="n">
+        <v>538</v>
+      </c>
+      <c r="E75" t="n">
+        <v>125</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="G75" t="n">
+        <v>33</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>4.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>26</v>
+      </c>
+      <c r="K75" t="n">
+        <v>19</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.20125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.05000000000000004</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.3500000000000014</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01817237798546212</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.117647058823529</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.879999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1796631316281971</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
